--- a/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,204 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>h_01JZW9E9B6ZZRTWQSYHXT2DAAF</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01JZW9E9B6ZZRTWQSYHXT2DAAF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Integration Setup</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Create Integration</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Integration Features</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Execution Settings</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Execution Settings</t>
+          <t>Execution General Settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,6 +636,72 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HR Employees Management</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Correlation Settings</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Entra ID Filter Settings</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KHNF6GCPFY005B8J072PHD1H</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNF6GCPFY005B8J072PHD1H</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KHNF6GCPFY005B8J072PHD1H</t>
+          <t>h_01KHNGPVKZAMRPTD9EGV8M4YDJ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNF6GCPFY005B8J072PHD1H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNGPVKZAMRPTD9EGV8M4YDJ</t>
         </is>
       </c>
     </row>

--- a/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,12 +693,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KHNGPVKZAMRPTD9EGV8M4YDJ</t>
+          <t>h_01KHNNEN2G9XFXRB20YTC3TEQC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNGPVKZAMRPTD9EGV8M4YDJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNNEN2G9XFXRB20YTC3TEQC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Provisioning Settings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KHNMP7V37BGNDT0PQTYGM99V</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNMP7V37BGNDT0PQTYGM99V</t>
         </is>
       </c>
     </row>

--- a/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,12 +693,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KHNNEN2G9XFXRB20YTC3TEQC</t>
+          <t>h_01KHNR86JVZTAQ5FH2VMSSCEZ5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNNEN2G9XFXRB20YTC3TEQC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JVZTAQ5FH2VMSSCEZ5</t>
         </is>
       </c>
     </row>
@@ -721,6 +721,138 @@
       <c r="D14" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNMP7V37BGNDT0PQTYGM99V</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Manage System Users User Management</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KHNR86JV2C5NYT9NXFEYKSVJ</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JV2C5NYT9NXFEYKSVJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Correlation Settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KHNR86JVFMC64ERZV9VCKCEH</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JVFMC64ERZV9VCKCEH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Entra ID Filter Settings</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Provisioning Settings</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Notifications Settings</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Notification Report Settings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
         </is>
       </c>
     </row>

--- a/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prerequisites</t>
+          <t>Key Functions</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,19 +473,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+          <t>h_01KG4G8M52X0H1382BKQAJQG71</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KG4G8M52X0H1382BKQAJQG71</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Integration Setup</t>
+          <t>Prerequisites</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,41 +495,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>h_01JZW70JA70W2SCAXXM5NFYAK0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01JZW70JA70W2SCAXXM5NFYAK0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Create Integration</t>
+          <t>Integration Setup</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Create Integration</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -539,41 +539,41 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,41 +583,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Integration Features</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Execution General Settings</t>
+          <t>Integration Features</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,63 +627,63 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HR Employees Management</t>
+          <t>Execution General Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>HR Employees Management</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Entra ID Filter Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KHNR86JVZTAQ5FH2VMSSCEZ5</t>
+          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JVZTAQ5FH2VMSSCEZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Entra ID Filter Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,63 +715,63 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KHNMP7V37BGNDT0PQTYGM99V</t>
+          <t>h_01KHNR86JVZTAQ5FH2VMSSCEZ5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNMP7V37BGNDT0PQTYGM99V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JVZTAQ5FH2VMSSCEZ5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Manage System Users User Management</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KHNR86JV2C5NYT9NXFEYKSVJ</t>
+          <t>h_01KHNMP7V37BGNDT0PQTYGM99V</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JV2C5NYT9NXFEYKSVJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNMP7V37BGNDT0PQTYGM99V</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Manage System Users User Management</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KHNR86JVFMC64ERZV9VCKCEH</t>
+          <t>h_01KHNR86JV2C5NYT9NXFEYKSVJ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JVFMC64ERZV9VCKCEH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JV2C5NYT9NXFEYKSVJ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Entra ID Filter Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
+          <t>h_01KHNR86JVFMC64ERZV9VCKCEH</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JVFMC64ERZV9VCKCEH</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Entra ID Filter Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,56 +803,342 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
+          <t>h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notifications Settings</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Notifications Settings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Notification Report Settings</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Notification Template For User Creation Email Notification Settings</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KHQKJMWEZVMGF28GXHPD1N8J</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHQKJMWEZVMGF28GXHPD1N8J</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KGHF9JDXCJXF0HYB7BRZ2P0E</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHF9JDXCJXF0HYB7BRZ2P0E</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Log Insight Settings</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KGHFA6Y71CG6DK6D0DZ6XTH1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHFA6Y71CG6DK6D0DZ6XTH1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>

--- a/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HR Employees Management</t>
+          <t>Employee Management</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KHQKJMWEZVMGF28GXHPD1N8J</t>
+          <t>h_01KJCMRKSE0W5613S8ZP0JT8S5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHQKJMWEZVMGF28GXHPD1N8J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KJCMRKSE0W5613S8ZP0JT8S5</t>
         </is>
       </c>
     </row>

--- a/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -749,51 +749,51 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Manage System Users User Management</t>
+          <t>Provisioning Threshold</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KHNR86JV2C5NYT9NXFEYKSVJ</t>
+          <t>h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JV2C5NYT9NXFEYKSVJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Manage System Users User Management</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KHNR86JVFMC64ERZV9VCKCEH</t>
+          <t>h_01KHNR86JV2C5NYT9NXFEYKSVJ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JVFMC64ERZV9VCKCEH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JV2C5NYT9NXFEYKSVJ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Entra ID Filter Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
+          <t>h_01KHNR86JVFMC64ERZV9VCKCEH</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JVFMC64ERZV9VCKCEH</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Entra ID Filter Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,41 +825,41 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
+          <t>h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notifications Settings</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KJCPW6MERQ8P2DRXNWYSVDB6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KJCPW6MERQ8P2DRXNWYSVDB6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Provisioning Threshold</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,63 +869,63 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
+          <t>h_01KJCPW6MEAMJ48M1XE38XBQKS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KJCPW6MEAMJ48M1XE38XBQKS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notification Template For User Creation Email Notification Settings</t>
+          <t>Notifications Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KJCMRKSE0W5613S8ZP0JT8S5</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KJCMRKSE0W5613S8ZP0JT8S5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Notification Template For User Creation Email Notification Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KGHF9JDXCJXF0HYB7BRZ2P0E</t>
+          <t>h_01KJCPW6MEZY7DAH42BQCP2KD7</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHF9JDXCJXF0HYB7BRZ2P0E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KJCPW6MEZY7DAH42BQCP2KD7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KGHFA6Y71CG6DK6D0DZ6XTH1</t>
+          <t>h_01KGHF9JDXCJXF0HYB7BRZ2P0E</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHFA6Y71CG6DK6D0DZ6XTH1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHF9JDXCJXF0HYB7BRZ2P0E</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,63 +1023,63 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+          <t>h_01KGHFA6Y71CG6DK6D0DZ6XTH1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHFA6Y71CG6DK6D0DZ6XTH1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,54 +1089,98 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Employee Management</t>
+          <t>HR Workers Management</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Manage System Users User Management</t>
+          <t>Manage System Users System Users Management</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -847,12 +847,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KJCPW6MERQ8P2DRXNWYSVDB6</t>
+          <t>h_01KJCSZ76EHRYTAC6GARWBPXWK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KJCPW6MERQ8P2DRXNWYSVDB6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KJCSZ76EHRYTAC6GARWBPXWK</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KJCPW6MEAMJ48M1XE38XBQKS</t>
+          <t>h_01KJCSZ76EZXHZKE1TQS5K186B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KJCPW6MEAMJ48M1XE38XBQKS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KJCSZ76EZXHZKE1TQS5K186B</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KJCPW6MEZY7DAH42BQCP2KD7</t>
+          <t>h_01KJCSZ76EG6G02NECNPM0QZ80</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KJCPW6MEZY7DAH42BQCP2KD7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KJCSZ76EG6G02NECNPM0QZ80</t>
         </is>
       </c>
     </row>

--- a/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Execution General Settings</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -969,29 +969,29 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KGHF9JDXCJXF0HYB7BRZ2P0E</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHF9JDXCJXF0HYB7BRZ2P0E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,63 +1023,63 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KGHFA6Y71CG6DK6D0DZ6XTH1</t>
+          <t>h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHFA6Y71CG6DK6D0DZ6XTH1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,98 +1089,54 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Execute Integration</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Manage System Users System Users Management</t>
+          <t>System Users Management</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">

--- a/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -781,12 +781,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KHNR86JV2C5NYT9NXFEYKSVJ</t>
+          <t>h_01KKBMXVHB7WJDCHSC4ACBW4XT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KHNR86JV2C5NYT9NXFEYKSVJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KKBMXVHB7WJDCHSC4ACBW4XT</t>
         </is>
       </c>
     </row>

--- a/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Microsoft-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -881,7 +881,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notifications Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -925,7 +925,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Notification Template For User Creation Email Notification Settings</t>
+          <t>Email Notification Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
